--- a/FINAL450.xlsx
+++ b/FINAL450.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MANJIT KUMAR JAGOAR\Desktop\c++\DSA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bhara\OneDrive\Desktop\Data-structure\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16088886-06D6-467C-9A09-4F91397050FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F3B08AB-D8BB-4535-AB1E-6F8F0C1DA80A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{261C335C-1D91-C143-AEEF-19B82073468C}"/>
   </bookViews>
@@ -1900,7 +1900,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>4</v>
+        <v>465</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="21">
